--- a/data/trans_dic/P37A$otros-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P37A$otros-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,15</t>
+          <t>0,5; 3,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,14</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,92</t>
+          <t>0,5; 4,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,99</t>
+          <t>0,4; 2,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,21</t>
+          <t>0,33; 3,11</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 0,82</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,87</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,87</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,22 +882,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 2,29</t>
+          <t>0,22; 2,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,75</t>
+          <t>0,08; 0,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,66</t>
+          <t>0,23; 1,65</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,88</t>
+          <t>0,16; 1,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,18</t>
+          <t>0,67; 3,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,91</t>
+          <t>0,15; 1,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,04</t>
+          <t>0,62; 2,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,57</t>
+          <t>0,07; 0,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,31</t>
+          <t>0,26; 1,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,12</t>
+          <t>0,75; 2,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,55</t>
+          <t>0,33; 1,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,79</t>
+          <t>0,5; 1,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,36</t>
+          <t>0,52; 1,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,03</t>
+          <t>0,33; 2,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,17 +1302,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,22</t>
+          <t>0,65; 2,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,76</t>
+          <t>0,67; 1,73</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,27</t>
+          <t>0,7; 3,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,15</t>
+          <t>0,23; 1,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,54</t>
+          <t>0,62; 1,99</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,18</t>
+          <t>0,13; 1,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,98</t>
+          <t>0,15; 0,92</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1697,27 +1697,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,26</t>
+          <t>0,03; 0,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,22</t>
+          <t>0,0; 0,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,71</t>
+          <t>0,2; 0,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,28</t>
+          <t>0,62; 1,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,3</t>
+          <t>0,03; 0,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,32 +1727,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,57</t>
+          <t>0,17; 0,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,29</t>
+          <t>0,78; 1,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,23</t>
+          <t>0,06; 0,24</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,2</t>
+          <t>0,05; 0,23</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,52</t>
+          <t>0,22; 0,53</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,18</t>
+          <t>0,77; 1,26</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>9602</t>
         </is>
       </c>
     </row>
@@ -2073,57 +2073,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5449</t>
+          <t>0; 4829</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2105; 13194</t>
+          <t>2112; 12761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 16554</t>
+          <t>0; 12236</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>0; 4409</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5677</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8877</t>
+          <t>0; 11100</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>325; 15398</t>
+          <t>1830; 18035</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4400</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 6885</t>
+          <t>0; 5994</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3177; 16224</t>
+          <t>3235; 16976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1963; 22897</t>
+          <t>2522; 23989</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6609</t>
         </is>
       </c>
     </row>
@@ -2276,22 +2276,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7719</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6005</t>
+          <t>0; 5651</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 5148</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7269</t>
+          <t>0; 9973</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2301,37 +2301,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5171</t>
+          <t>0; 5913</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6842</t>
+          <t>0; 5974</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>808; 11729</t>
+          <t>1082; 12920</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5790</t>
+          <t>0; 6459</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6150</t>
+          <t>0; 6073</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>884; 8601</t>
+          <t>887; 7764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1986; 15574</t>
+          <t>2208; 16159</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>16597</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6184</t>
+          <t>0; 5919</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1058; 12578</t>
+          <t>1060; 11628</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3445; 17056</t>
+          <t>4154; 20261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4891</t>
+          <t>0; 4589</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2514,17 +2514,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1003; 12648</t>
+          <t>1000; 11038</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3248; 12101</t>
+          <t>3880; 13904</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>869; 7583</t>
+          <t>869; 8176</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3442; 17469</t>
+          <t>3481; 18100</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8277; 23907</t>
+          <t>9370; 26373</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>13076</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1504; 13742</t>
+          <t>2325; 13758</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4971</t>
+          <t>0; 5565</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3947; 12780</t>
+          <t>3720; 12073</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4968</t>
+          <t>0; 4980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6854; 21783</t>
+          <t>7461; 21205</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>13418</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1901; 11386</t>
+          <t>2014; 12164</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7448</t>
+          <t>0; 5968</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4831</t>
+          <t>0; 4230</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3562; 12179</t>
+          <t>3960; 12917</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2945,17 +2945,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 7038</t>
+          <t>0; 6275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7203</t>
+          <t>0; 6255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7130; 19501</t>
+          <t>8147; 21126</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>9498</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4250</t>
+          <t>0; 3900</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2444; 12048</t>
+          <t>2856; 12862</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3133,37 +3133,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>0; 4702</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6752</t>
+          <t>0; 7533</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>584; 7013</t>
+          <t>1015; 7050</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4088</t>
+          <t>0; 4611</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4650</t>
+          <t>0; 3780</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5681</t>
+          <t>0; 6625</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3393; 15084</t>
+          <t>5243; 16810</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3233</t>
         </is>
       </c>
     </row>
@@ -3326,22 +3326,22 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5683</t>
+          <t>0; 5684</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4330</t>
+          <t>0; 4688</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7909</t>
+          <t>0; 7284</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7041</t>
+          <t>0; 5923</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3351,27 +3351,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>565; 5042</t>
+          <t>592; 5737</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 6621</t>
+          <t>0; 7488</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5878</t>
+          <t>0; 4718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 5341</t>
+          <t>0; 5647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1124; 6946</t>
+          <t>1128; 7138</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>34830</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>72034</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>880; 8415</t>
+          <t>876; 8839</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7488</t>
+          <t>0; 6756</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6929; 23930</t>
+          <t>6729; 23249</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19346; 44262</t>
+          <t>22044; 47690</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>986; 10156</t>
+          <t>984; 10786</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1951; 11884</t>
+          <t>1950; 11838</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5934; 20233</t>
+          <t>5963; 20430</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>24327; 47813</t>
+          <t>29078; 55356</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3806; 15158</t>
+          <t>3725; 15682</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3000; 14019</t>
+          <t>3192; 15800</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15227; 36172</t>
+          <t>15150; 36591</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>49201; 84626</t>
+          <t>56208; 91698</t>
         </is>
       </c>
     </row>
